--- a/LubanConfig/Moba/Production/Datas/J-投射物表.xlsx
+++ b/LubanConfig/Moba/Production/Datas/J-投射物表.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1056,6 +1056,306 @@
       <c r="I18" s="2" t="n"/>
       <c r="J18" s="2" t="n"/>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n">
+        <v>31070001</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Linear</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>嬴政-普通攻击-单发飞剑发射器</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n">
+        <v>31070301</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Linear</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>嬴政-至尊王权-飞剑发射器</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="2" t="n">
+        <v>31070201</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Linear</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>墨子-机关重炮-单发炮弹发射器</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="2" t="n">
+        <v>31070202</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Linear</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>SunShangxiang Skill2 Launcher</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n">
+        <v>31070302</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Linear</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>SunShangxiang Skill3 Launcher</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n">
+        <v>31080001</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Linear</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>鲁班七号-普通攻击发射器</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="2" t="n">
+        <v>31080101</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Linear</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>鲁班七号-河豚手雷发射器</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n"/>
+      <c r="B26" s="2" t="n">
+        <v>31080201</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Linear</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>鲁班七号-无敌鲨嘴炮发射器</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="2" t="n">
+        <v>31080301</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Linear</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>鲁班七号-扫射发射器</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="2" t="n">
+        <v>31080401</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Linear</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>鲁班七号-召唤物投弹发射器</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n"/>
+      <c r="J28" s="2" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1067,7 +1367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB15"/>
+  <dimension ref="A1:AB25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2416,6 +2716,798 @@
       </c>
       <c r="AB15" s="2" t="n"/>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="2" t="n">
+        <v>30070001</v>
+      </c>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Pierce</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>嬴政-普通攻击-飞剑投射物</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>10070011</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="2" t="n"/>
+      <c r="U16" s="2" t="n"/>
+      <c r="V16" s="2" t="n"/>
+      <c r="W16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="X16" s="2" t="n"/>
+      <c r="Y16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="2" t="n">
+        <v>90006011</v>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>CollisionHeight,CollisionLength,CollisionWidth,OnExitTriggerIds,SpawnRandomOffsetX,SpawnRandomOffsetY,SpawnRandomOffsetZ,StateMachineProfileId</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="2" t="n">
+        <v>30070301</v>
+      </c>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Pierce</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>嬴政-至尊王权-飞剑投射物</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n"/>
+      <c r="M17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>10070313</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>ying_zheng_ultimate_projectile</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z17" s="2" t="n">
+        <v>90006003</v>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>CollisionHeight,CollisionLength,CollisionWidth,OnExitTriggerIds</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="2" t="n">
+        <v>30070201</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Pierce</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>墨子-机关重炮-炮弹投射物</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>10070211</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="2" t="n"/>
+      <c r="U18" s="2" t="n"/>
+      <c r="V18" s="2" t="n"/>
+      <c r="W18" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="X18" s="2" t="n"/>
+      <c r="Y18" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z18" s="2" t="n">
+        <v>90004002</v>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>SpawnRandomOffsetX,SpawnRandomOffsetY,SpawnRandomOffsetZ,StateMachineProfileId</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n">
+        <v>30070202</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Pierce</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>SunShangxiang Skill2 Projectile</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>10070211</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="2" t="n"/>
+      <c r="U19" s="2" t="n"/>
+      <c r="V19" s="2" t="n"/>
+      <c r="W19" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="X19" s="2" t="n"/>
+      <c r="Y19" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z19" s="2" t="n">
+        <v>90003002</v>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>SpawnRandomOffsetX,SpawnRandomOffsetY,SpawnRandomOffsetZ,StateMachineProfileId</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n">
+        <v>30070302</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Pierce</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>SunShangxiang Skill3 Projectile</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>10070313</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="X20" s="2" t="n"/>
+      <c r="Y20" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z20" s="2" t="n">
+        <v>90003003</v>
+      </c>
+      <c r="AA20" s="2" t="n"/>
+      <c r="AB20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="2" t="n">
+        <v>30080001</v>
+      </c>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Pierce</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>鲁班七号-普通攻击投射物</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="n"/>
+      <c r="M21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>10080012</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="2" t="n"/>
+      <c r="U21" s="2" t="n"/>
+      <c r="V21" s="2" t="n"/>
+      <c r="W21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="X21" s="2" t="n"/>
+      <c r="Y21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>CollisionHeight,CollisionLength,CollisionWidth,OnExitTriggerIds,SpawnRandomOffsetX,SpawnRandomOffsetY,SpawnRandomOffsetZ,StateMachineProfileId</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="2" t="n">
+        <v>30080101</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Pierce</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>鲁班七号-河豚手雷投射物</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>10080111</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>10080111</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="2" t="n"/>
+      <c r="U22" s="2" t="n"/>
+      <c r="V22" s="2" t="n"/>
+      <c r="W22" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="X22" s="2" t="n"/>
+      <c r="Y22" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>SpawnRandomOffsetX,SpawnRandomOffsetY,SpawnRandomOffsetZ,StateMachineProfileId</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n">
+        <v>30080201</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Pierce</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>鲁班七号-无敌鲨嘴炮投射物</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n"/>
+      <c r="M23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>10080211</v>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="X23" s="2" t="n"/>
+      <c r="Y23" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="2" t="n"/>
+      <c r="AB23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n">
+        <v>30080301</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Pierce</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>鲁班七号-扫射投射物</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n"/>
+      <c r="M24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>10080004</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="X24" s="2" t="n"/>
+      <c r="Y24" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="2" t="n"/>
+      <c r="AB24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="2" t="n">
+        <v>30080401</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Pierce</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>鲁班七号-空中支援炸弹</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n"/>
+      <c r="M25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>10080411</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="X25" s="2" t="n"/>
+      <c r="Y25" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="2" t="n"/>
+      <c r="AB25" s="2" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2427,7 +3519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T20"/>
+  <dimension ref="A1:T25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3759,6 +4851,312 @@
         </is>
       </c>
       <c r="T20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="2" t="n">
+        <v>40070101</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>90000101</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>嬴政-王者惩戒-目标点剑阵区域</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>10070111</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="n"/>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>10070111</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>90006001</v>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>OnEnterTriggerIds</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="2" t="n">
+        <v>40070201</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>90000101</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>嬴政-王者守御-自身清场区域</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>10070211</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="n"/>
+      <c r="P22" s="2" t="n"/>
+      <c r="Q22" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>90006002</v>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>IntervalMs,OnEnterTriggerIds,OnIntervalTriggerIds</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n">
+        <v>40070202</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>90000101</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>墨子-机关重炮-弹坑持续伤害区域</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>10070212</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="n"/>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>10070212</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>90004004</v>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>OnEnterTriggerIds</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n">
+        <v>40070203</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>90000101</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>SunShangxiang Skill2 Explosion Area</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>10070212</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="n"/>
+      <c r="P24" s="2" t="n"/>
+      <c r="Q24" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>90003002</v>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>OnEnterTriggerIds,OnIntervalTriggerIds</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="2" t="n">
+        <v>40080101</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>90000101</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>鲁班七号-河豚手雷-爆炸区域</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>10080112</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="n"/>
+      <c r="P25" s="2" t="n"/>
+      <c r="Q25" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>90003002</v>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>OnEnterTriggerIds,OnIntervalTriggerIds</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/LubanConfig/Moba/Production/Datas/J-投射物表.xlsx
+++ b/LubanConfig/Moba/Production/Datas/J-投射物表.xlsx
@@ -436,7 +436,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -1368,7 +1368,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AB25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -2351,9 +2351,15 @@
       <c r="B11" s="2" t="n">
         <v>30060301</v>
       </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
+      <c r="C11" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0.8</v>
+      </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
@@ -2423,7 +2429,7 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>CollisionHeight,CollisionLength,CollisionWidth,OnExitTriggerIds</t>
+          <t>OnExitTriggerIds</t>
         </is>
       </c>
       <c r="AB11" s="2" t="n"/>
@@ -3025,7 +3031,7 @@
         <v>33</v>
       </c>
       <c r="Z19" s="2" t="n">
-        <v>90003002</v>
+        <v>90007002</v>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
@@ -3070,7 +3076,11 @@
           <t>SunShangxiang Skill3 Projectile</t>
         </is>
       </c>
-      <c r="L20" s="2" t="n"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>10070311</t>
+        </is>
+      </c>
       <c r="M20" s="2" t="n">
         <v>0</v>
       </c>
@@ -3109,7 +3119,7 @@
         <v>33</v>
       </c>
       <c r="Z20" s="2" t="n">
-        <v>90003003</v>
+        <v>90007004</v>
       </c>
       <c r="AA20" s="2" t="n"/>
       <c r="AB20" s="2" t="n"/>
@@ -3127,11 +3137,11 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Pierce</t>
+          <t>ExitOnHit</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I21" s="2" t="n">
         <v>1000</v>
@@ -3177,7 +3187,7 @@
         <v>0</v>
       </c>
       <c r="Z21" s="2" t="n">
-        <v>0</v>
+        <v>90008001</v>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
@@ -3259,7 +3269,7 @@
         <v>33</v>
       </c>
       <c r="Z22" s="2" t="n">
-        <v>0</v>
+        <v>90008002</v>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
@@ -3291,7 +3301,7 @@
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I23" s="2" t="n">
         <v>1800</v>
@@ -3343,7 +3353,7 @@
         <v>33</v>
       </c>
       <c r="Z23" s="2" t="n">
-        <v>0</v>
+        <v>90008004</v>
       </c>
       <c r="AA23" s="2" t="n"/>
       <c r="AB23" s="2" t="n"/>
@@ -3371,7 +3381,7 @@
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I24" s="2" t="n">
         <v>1800</v>
@@ -3423,7 +3433,7 @@
         <v>33</v>
       </c>
       <c r="Z24" s="2" t="n">
-        <v>0</v>
+        <v>90008005</v>
       </c>
       <c r="AA24" s="2" t="n"/>
       <c r="AB24" s="2" t="n"/>
@@ -3503,7 +3513,7 @@
         <v>33</v>
       </c>
       <c r="Z25" s="2" t="n">
-        <v>0</v>
+        <v>90008006</v>
       </c>
       <c r="AA25" s="2" t="n"/>
       <c r="AB25" s="2" t="n"/>
@@ -3519,8 +3529,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:T27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -4011,7 +4021,7 @@
         <v>4.5</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0</v>
+        <v>90001003</v>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
@@ -4069,7 +4079,7 @@
         <v>4.5</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0</v>
+        <v>90001003</v>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
@@ -4127,7 +4137,7 @@
         <v>4.5</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0</v>
+        <v>90001003</v>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
@@ -5089,7 +5099,7 @@
         <v>4</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>90003002</v>
+        <v>90007003</v>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
@@ -5146,10 +5156,10 @@
       <c r="O25" s="2" t="n"/>
       <c r="P25" s="2" t="n"/>
       <c r="Q25" s="2" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R25" s="2" t="n">
-        <v>90003002</v>
+        <v>90008003</v>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
@@ -5157,6 +5167,126 @@
         </is>
       </c>
       <c r="T25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n"/>
+      <c r="B26" s="2" t="n">
+        <v>40070301</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>90000101</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>孙尚香-究极弩炮-爆炸范围</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>10070314</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="n"/>
+      <c r="P26" s="2" t="n"/>
+      <c r="Q26" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>90007003</v>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>OnEnterTriggerIds,OnIntervalTriggerIds</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="2" t="n">
+        <v>40080401</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>650</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>90000101</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>鲁班七号-空中支援-定时轰炸范围</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>10080412</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="n"/>
+      <c r="P27" s="2" t="n"/>
+      <c r="Q27" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>90008006</v>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>OnEnterTriggerIds,OnIntervalTriggerIds</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5170,7 +5300,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Q5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
